--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03F4ABD0-5E0C-42DD-9969-A8E41334665B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D31EF95-FF40-4D22-818D-85394151984D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4A97C90-7BAF-404A-9C70-6792ED002DAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF09107-F4BD-45A0-8B81-0C34980BA490}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A1E6A1-46AC-48C7-80F4-95D48CB810D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A75307C-9C27-49C9-8DEE-764DD072BB16}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D31EF95-FF40-4D22-818D-85394151984D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96A89A9-C6EC-4748-9A5B-B1AEC8D90E40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF09107-F4BD-45A0-8B81-0C34980BA490}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA0D0818-8B6D-4C75-B4A2-F3643AC4BB34}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A75307C-9C27-49C9-8DEE-764DD072BB16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3999D837-4B0C-4A65-83C8-2F7003270F2C}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96A89A9-C6EC-4748-9A5B-B1AEC8D90E40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42A7A1C1-6DB9-4560-8C95-3DC0A5E8A64E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA0D0818-8B6D-4C75-B4A2-F3643AC4BB34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0D1B8C-0387-45F1-B0D9-130B691AC534}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3999D837-4B0C-4A65-83C8-2F7003270F2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC827EBA-8BB4-42C4-813C-0DA28CF748CE}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42A7A1C1-6DB9-4560-8C95-3DC0A5E8A64E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD2189C-BF4B-454A-99F8-846A98382899}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0D1B8C-0387-45F1-B0D9-130B691AC534}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C59C236C-6DDC-40EC-A54C-8E3B56EA5DC5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC827EBA-8BB4-42C4-813C-0DA28CF748CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFAC48E1-C0A4-4214-9293-9C14396AE1D8}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95549BC3-9FF1-4AA2-9BFC-21D97DDC5AEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E1448C-E078-4DB9-B8EF-5875C2542298}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1780ED9C-7F12-44EA-8136-3252AB8DB91B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB0F4D0-8451-4C13-8FAD-8779E4FFA134}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA282C4B-1C88-41B7-8250-7389BD567959}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAD531B2-E45E-4ADB-8A4B-D5FBB453BA3A}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E1448C-E078-4DB9-B8EF-5875C2542298}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FB7A0FF-A8A3-48ED-9DDB-80C7064144D2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB0F4D0-8451-4C13-8FAD-8779E4FFA134}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5A9DF4D-665C-4901-82FC-25F66504713C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAD531B2-E45E-4ADB-8A4B-D5FBB453BA3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DDEF06E-4FC0-4905-A135-292405BDF8F2}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3623,291 +3623,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FB7A0FF-A8A3-48ED-9DDB-80C7064144D2}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5A9DF4D-665C-4901-82FC-25F66504713C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DDEF06E-4FC0-4905-A135-292405BDF8F2}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3623,4 +3623,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93BD4A8E-E3E0-420B-B8C6-812EEDFF07AB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1873470-CDD9-43C6-BBC3-957541B0E0B9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10EED1C8-4243-42B0-8E2B-BB6C6F6DDE23}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3623,291 +3623,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93BD4A8E-E3E0-420B-B8C6-812EEDFF07AB}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1873470-CDD9-43C6-BBC3-957541B0E0B9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10EED1C8-4243-42B0-8E2B-BB6C6F6DDE23}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3623,4 +3623,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3EC335C-83B9-4542-BB4D-8C189FD948B9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8FE4BAD-0A56-4695-ABD8-7D416C67813C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2943DD-1435-43C8-9C96-244ABE06400F}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3EC335C-83B9-4542-BB4D-8C189FD948B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C3668D8-4CE0-4182-B77C-19FA490BDEA8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8FE4BAD-0A56-4695-ABD8-7D416C67813C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9760D407-2BE5-4B18-9E87-B42BC4B15B6B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2943DD-1435-43C8-9C96-244ABE06400F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7EE0A10-B8E6-48E8-B265-1E47F80EFCF8}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C3668D8-4CE0-4182-B77C-19FA490BDEA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD8D9A9-E24F-4BB0-AF9B-DAB5A78A64EE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9760D407-2BE5-4B18-9E87-B42BC4B15B6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FD10380-0CCB-487F-B63E-20740748AA76}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7EE0A10-B8E6-48E8-B265-1E47F80EFCF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E7D9868-6562-4AF5-A773-325F35596DC3}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD8D9A9-E24F-4BB0-AF9B-DAB5A78A64EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2CE1FA8-A534-47CE-8B16-ECF21458D312}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FD10380-0CCB-487F-B63E-20740748AA76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{510D2A54-8B00-4B94-BA1B-3A54D96F36ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E7D9868-6562-4AF5-A773-325F35596DC3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F14447EF-B1C5-4DA7-96E6-5ADBABDCA33C}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2CE1FA8-A534-47CE-8B16-ECF21458D312}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8464C8FC-A9E0-45FF-A212-627DA8B24701}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{510D2A54-8B00-4B94-BA1B-3A54D96F36ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE47B5EE-62A2-4A23-8F0E-7178EC9EFA1F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F14447EF-B1C5-4DA7-96E6-5ADBABDCA33C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{668E69AE-D662-4F55-B875-369AEC255F90}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8464C8FC-A9E0-45FF-A212-627DA8B24701}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0038FFE1-4A03-475F-A3DF-B55E570C58B3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE47B5EE-62A2-4A23-8F0E-7178EC9EFA1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77AB3754-903E-4153-A386-6A0AFF36323E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{668E69AE-D662-4F55-B875-369AEC255F90}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BE7C174-6047-4C46-BE3F-28B50FEE01C7}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3623,291 +3623,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0038FFE1-4A03-475F-A3DF-B55E570C58B3}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77AB3754-903E-4153-A386-6A0AFF36323E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BE7C174-6047-4C46-BE3F-28B50FEE01C7}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3623,4 +3623,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00F46BF2-5E66-4BFD-85B5-3F1A314945A8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35DC0F00-A3D9-438E-BABE-2A204AEC60AA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE5654F-0019-432D-889A-936331BD804F}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="166">
   <si>
     <t>species_sci</t>
   </si>
@@ -407,9 +407,6 @@
   </si>
   <si>
     <t>NMW 22755</t>
-  </si>
-  <si>
-    <t>Trachypithecus cristatus</t>
   </si>
   <si>
     <t>Presbytis cristata</t>
@@ -3025,10 +3022,10 @@
         <v>131</v>
       </c>
       <c r="B109" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109" t="s">
         <v>132</v>
-      </c>
-      <c r="C109" t="s">
-        <v>133</v>
       </c>
       <c r="D109" t="s">
         <v>62</v>
@@ -3045,10 +3042,10 @@
         <v>131</v>
       </c>
       <c r="B110" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C110" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D110" t="s">
         <v>62</v>
@@ -3065,10 +3062,10 @@
         <v>131</v>
       </c>
       <c r="B111" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C111" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D111" t="s">
         <v>62</v>
@@ -3085,10 +3082,10 @@
         <v>131</v>
       </c>
       <c r="B112" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C112" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D112" t="s">
         <v>62</v>
@@ -3105,10 +3102,10 @@
         <v>131</v>
       </c>
       <c r="B113" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C113" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -3125,10 +3122,10 @@
         <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C114" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D114" t="s">
         <v>62</v>
@@ -3145,10 +3142,10 @@
         <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D115" t="s">
         <v>62</v>
@@ -3165,10 +3162,10 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C116" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D116" t="s">
         <v>62</v>
@@ -3185,10 +3182,10 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C117" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D117" t="s">
         <v>62</v>
@@ -3202,13 +3199,13 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
+        <v>141</v>
+      </c>
+      <c r="B118" t="s">
+        <v>141</v>
+      </c>
+      <c r="C118" t="s">
         <v>142</v>
-      </c>
-      <c r="B118" t="s">
-        <v>142</v>
-      </c>
-      <c r="C118" t="s">
-        <v>143</v>
       </c>
       <c r="D118" t="s">
         <v>8</v>
@@ -3222,13 +3219,13 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C119" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D119" t="s">
         <v>8</v>
@@ -3242,13 +3239,13 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B120" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C120" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D120" t="s">
         <v>8</v>
@@ -3262,13 +3259,13 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B121" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C121" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D121" t="s">
         <v>62</v>
@@ -3282,16 +3279,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B122" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C122" t="s">
+        <v>146</v>
+      </c>
+      <c r="D122" t="s">
         <v>147</v>
-      </c>
-      <c r="D122" t="s">
-        <v>148</v>
       </c>
       <c r="E122">
         <v>0.0073</v>
@@ -3302,16 +3299,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B123" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C123" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D123" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E123">
         <v>0.0134</v>
@@ -3322,13 +3319,13 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
+        <v>149</v>
+      </c>
+      <c r="B124" t="s">
+        <v>149</v>
+      </c>
+      <c r="C124" t="s">
         <v>150</v>
-      </c>
-      <c r="B124" t="s">
-        <v>150</v>
-      </c>
-      <c r="C124" t="s">
-        <v>151</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -3342,13 +3339,13 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B125" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C125" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D125" t="s">
         <v>8</v>
@@ -3362,13 +3359,13 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B126" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D126" t="s">
         <v>8</v>
@@ -3382,13 +3379,13 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B127" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C127" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
@@ -3402,13 +3399,13 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B128" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C128" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D128" t="s">
         <v>8</v>
@@ -3422,13 +3419,13 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B129" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C129" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D129" t="s">
         <v>8</v>
@@ -3442,13 +3439,13 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B130" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C130" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D130" t="s">
         <v>8</v>
@@ -3462,13 +3459,13 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B131" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C131" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D131" t="s">
         <v>8</v>
@@ -3482,13 +3479,13 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C132" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D132" t="s">
         <v>8</v>
@@ -3502,13 +3499,13 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
+        <v>159</v>
+      </c>
+      <c r="B133" t="s">
+        <v>159</v>
+      </c>
+      <c r="C133" t="s">
         <v>160</v>
-      </c>
-      <c r="B133" t="s">
-        <v>160</v>
-      </c>
-      <c r="C133" t="s">
-        <v>161</v>
       </c>
       <c r="D133" t="s">
         <v>8</v>
@@ -3522,13 +3519,13 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B134" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C134" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D134" t="s">
         <v>8</v>
@@ -3542,13 +3539,13 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B135" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C135" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D135" t="s">
         <v>8</v>
@@ -3562,13 +3559,13 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B136" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D136" t="s">
         <v>8</v>
@@ -3582,13 +3579,13 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B137" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D137" t="s">
         <v>8</v>
@@ -3602,13 +3599,13 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B138" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C138" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D138" t="s">
         <v>8</v>
@@ -3901,13 +3898,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00F46BF2-5E66-4BFD-85B5-3F1A314945A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82DE955F-4990-4959-B447-FE7B2A5A00E0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35DC0F00-A3D9-438E-BABE-2A204AEC60AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD138CF-2648-4660-A660-F379ED499258}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE5654F-0019-432D-889A-936331BD804F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448C05FB-C0F5-4C6B-BD2B-09ACF23819BB}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3898,13 +3898,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82DE955F-4990-4959-B447-FE7B2A5A00E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{233A0CCF-B969-42BF-BA1A-68FCEA4F13E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD138CF-2648-4660-A660-F379ED499258}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33DBEFFF-076C-42D5-82D2-1B3A5629AC80}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448C05FB-C0F5-4C6B-BD2B-09ACF23819BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7661B6D2-AB7E-44E6-AEDF-DD20961ACFBE}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="167">
   <si>
     <t>species_sci</t>
   </si>
@@ -407,6 +407,9 @@
   </si>
   <si>
     <t>NMW 22755</t>
+  </si>
+  <si>
+    <t>Trachypithecus cristatus</t>
   </si>
   <si>
     <t>Presbytis cristata</t>
@@ -3022,10 +3025,10 @@
         <v>131</v>
       </c>
       <c r="B109" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D109" t="s">
         <v>62</v>
@@ -3042,10 +3045,10 @@
         <v>131</v>
       </c>
       <c r="B110" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C110" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D110" t="s">
         <v>62</v>
@@ -3062,10 +3065,10 @@
         <v>131</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C111" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D111" t="s">
         <v>62</v>
@@ -3082,10 +3085,10 @@
         <v>131</v>
       </c>
       <c r="B112" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C112" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D112" t="s">
         <v>62</v>
@@ -3102,10 +3105,10 @@
         <v>131</v>
       </c>
       <c r="B113" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C113" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -3122,10 +3125,10 @@
         <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C114" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D114" t="s">
         <v>62</v>
@@ -3142,10 +3145,10 @@
         <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C115" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D115" t="s">
         <v>62</v>
@@ -3162,10 +3165,10 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C116" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D116" t="s">
         <v>62</v>
@@ -3182,10 +3185,10 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C117" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D117" t="s">
         <v>62</v>
@@ -3199,13 +3202,13 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B118" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C118" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D118" t="s">
         <v>8</v>
@@ -3219,13 +3222,13 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D119" t="s">
         <v>8</v>
@@ -3239,13 +3242,13 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B120" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C120" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D120" t="s">
         <v>8</v>
@@ -3259,13 +3262,13 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B121" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C121" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D121" t="s">
         <v>62</v>
@@ -3279,16 +3282,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B122" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C122" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D122" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E122">
         <v>0.0073</v>
@@ -3299,16 +3302,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B123" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C123" t="s">
+        <v>149</v>
+      </c>
+      <c r="D123" t="s">
         <v>148</v>
-      </c>
-      <c r="D123" t="s">
-        <v>147</v>
       </c>
       <c r="E123">
         <v>0.0134</v>
@@ -3319,13 +3322,13 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B124" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C124" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -3339,13 +3342,13 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B125" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C125" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D125" t="s">
         <v>8</v>
@@ -3359,13 +3362,13 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B126" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C126" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D126" t="s">
         <v>8</v>
@@ -3379,13 +3382,13 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B127" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
@@ -3399,13 +3402,13 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B128" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C128" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D128" t="s">
         <v>8</v>
@@ -3419,13 +3422,13 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B129" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C129" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D129" t="s">
         <v>8</v>
@@ -3439,13 +3442,13 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B130" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C130" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D130" t="s">
         <v>8</v>
@@ -3459,13 +3462,13 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B131" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C131" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D131" t="s">
         <v>8</v>
@@ -3479,13 +3482,13 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B132" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C132" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D132" t="s">
         <v>8</v>
@@ -3499,13 +3502,13 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B133" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C133" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D133" t="s">
         <v>8</v>
@@ -3519,13 +3522,13 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B134" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C134" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D134" t="s">
         <v>8</v>
@@ -3539,13 +3542,13 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B135" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C135" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D135" t="s">
         <v>8</v>
@@ -3559,13 +3562,13 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B136" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C136" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D136" t="s">
         <v>8</v>
@@ -3579,13 +3582,13 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B137" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D137" t="s">
         <v>8</v>
@@ -3599,13 +3602,13 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B138" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C138" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D138" t="s">
         <v>8</v>
@@ -3898,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{233A0CCF-B969-42BF-BA1A-68FCEA4F13E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFE60762-31F5-4FDC-A9E4-A5CE3A318C9F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33DBEFFF-076C-42D5-82D2-1B3A5629AC80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7BEF14-DCA3-4EC5-8ED3-EAFF0318DB82}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7661B6D2-AB7E-44E6-AEDF-DD20961ACFBE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD5A46C8-970D-481D-8E8D-BD7336FD02B0}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFE60762-31F5-4FDC-A9E4-A5CE3A318C9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{036C69F6-7407-44A7-A11B-FB24C67AF27E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7BEF14-DCA3-4EC5-8ED3-EAFF0318DB82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AA348AD-4070-404C-AB21-0C126E1F6125}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD5A46C8-970D-481D-8E8D-BD7336FD02B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A31919-8883-4F70-ADFC-FE3FFCB9538F}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3901,13 +3901,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{036C69F6-7407-44A7-A11B-FB24C67AF27E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C05E4CE-6143-4E87-A25C-8A5E297B61D9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AA348AD-4070-404C-AB21-0C126E1F6125}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED288F6E-8967-44FE-B0AF-97E846A41740}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A31919-8883-4F70-ADFC-FE3FFCB9538F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12F4A62F-5024-47D3-AD97-C592AB6A0DC8}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3623,291 +3623,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C05E4CE-6143-4E87-A25C-8A5E297B61D9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED288F6E-8967-44FE-B0AF-97E846A41740}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12F4A62F-5024-47D3-AD97-C592AB6A0DC8}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -3623,4 +3623,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E172FF7A-3C9B-4BAA-B37F-743CBED06E83}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58034EBE-0932-413C-9CC8-826A4880AD47}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{837915C1-CE0B-4774-9176-CE1273ABCA33}"/>
 </file>